--- a/data/ADaM_Specification.xlsx
+++ b/data/ADaM_Specification.xlsx
@@ -6389,7 +6389,7 @@
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>What ADT represents: the event, or the reason for censoring.</t>
+          <t>What ADT represents. LITERAL VALUES for this study - event records: 'First treatment-emergent adverse event'; censored records: 'Censored at last dose'. The text is not standardised by ADaM, so a spec that only describes the meaning is not reproducible - pin the exact strings here.</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Why censored; populated on censored records only.</t>
+          <t>Why censored; populated on censored records only. LITERAL VALUE for this study: 'LAST DOSE'. As with EVNTDESC the wording is a study choice, not an ADaM requirement, so it is fixed here.</t>
         </is>
       </c>
     </row>
